--- a/source_data/Source_Data_7T_Fig4_5.xlsx
+++ b/source_data/Source_Data_7T_Fig4_5.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Spatial\code\paper\revision\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zyeon\Desktop\Spatial 분석\paper\NC_final_revision\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2DD672-1162-412C-B503-72D673A644F5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E594D50-5CE2-4D32-8345-4000EBA5B7E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig4e_on_off_retrieval" sheetId="2" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>Subject_ID</t>
   </si>
@@ -51,22 +51,34 @@
     <t>Sub_Post</t>
   </si>
   <si>
-    <t>NodeAttractionIndex</t>
+    <t>node_attraction_idx_resid</t>
   </si>
   <si>
-    <t>AvgDistanceError</t>
+    <t>DG_Ant_activation_resid</t>
   </si>
   <si>
-    <t>AntSubiculum_activation</t>
+    <t>DG_Post_activation_resid</t>
   </si>
   <si>
-    <t>x_plotted_resid</t>
+    <t>CA23_Ant_activation_resid</t>
   </si>
   <si>
-    <t>y_plotted_resid</t>
+    <t>CA23_Post_activation_resid</t>
   </si>
   <si>
-    <t>PostDG_activation</t>
+    <t>CA1_Ant_activation_resid</t>
+  </si>
+  <si>
+    <t>CA1_Post_activation_resid</t>
+  </si>
+  <si>
+    <t>Sub_Ant_activation_resid</t>
+  </si>
+  <si>
+    <t>Sub_Post_activation_resid</t>
+  </si>
+  <si>
+    <t>AvgDistanceError_resid</t>
   </si>
 </sst>
 </file>
@@ -1041,17 +1053,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" customWidth="1"/>
-    <col min="2" max="2" width="18.26953125" customWidth="1"/>
-    <col min="3" max="3" width="15.26953125" customWidth="1"/>
-    <col min="4" max="4" width="21.54296875" customWidth="1"/>
-    <col min="5" max="6" width="14.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1070,405 +1087,657 @@
       <c r="F1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>1.5890327155864359E-2</v>
+        <v>1.8370311897750874E-2</v>
       </c>
       <c r="C2">
-        <v>0.24367326534378794</v>
+        <v>-0.17217311044331374</v>
       </c>
       <c r="D2">
-        <v>0.37385574386931608</v>
+        <v>0.73887902925906923</v>
       </c>
       <c r="E2">
-        <v>1.8370311897750874E-2</v>
+        <v>0.99233857156331895</v>
       </c>
       <c r="F2">
+        <v>0.36798664944464377</v>
+      </c>
+      <c r="G2">
+        <v>-4.2990475136948425E-2</v>
+      </c>
+      <c r="H2">
+        <v>0.88240592561324871</v>
+      </c>
+      <c r="I2">
         <v>-8.9637544536725788E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J2">
+        <v>-0.37058752607836487</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>-2.0174117386022594E-3</v>
+        <v>3.7746864774143157E-2</v>
       </c>
       <c r="C3">
-        <v>0.30411797708162736</v>
+        <v>-1.2731010294152902</v>
       </c>
       <c r="D3">
-        <v>-0.83744507110968702</v>
+        <v>-0.54897336695270182</v>
       </c>
       <c r="E3">
-        <v>3.7746864774143157E-2</v>
+        <v>-2.0586354411454897</v>
       </c>
       <c r="F3">
+        <v>-0.29945265971090684</v>
+      </c>
+      <c r="G3">
+        <v>-3.0435403675486528E-2</v>
+      </c>
+      <c r="H3">
+        <v>-0.7896117799678336</v>
+      </c>
+      <c r="I3">
         <v>-0.97742453370573568</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J3">
+        <v>-1.2511460242396857</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>-0.21838154673349786</v>
+        <v>-0.17527857527829885</v>
       </c>
       <c r="C4">
-        <v>0.30953061719874286</v>
+        <v>-0.66262255091246114</v>
       </c>
       <c r="D4">
-        <v>-1.5861544875827538</v>
+        <v>-4.9569654389761353E-2</v>
       </c>
       <c r="E4">
-        <v>-0.17527857527829885</v>
+        <v>-3.3163491395375506</v>
       </c>
       <c r="F4">
+        <v>-2.7427113618588339</v>
+      </c>
+      <c r="G4">
+        <v>-1.6860222145434298</v>
+      </c>
+      <c r="H4">
+        <v>1.7513761715535137</v>
+      </c>
+      <c r="I4">
         <v>-1.6971642709185986</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J4">
+        <v>1.5660798834237071</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>-2.4515624912984091E-2</v>
+        <v>-6.5740576798610298E-2</v>
       </c>
       <c r="C5">
-        <v>0.17281950440322735</v>
+        <v>0.20488201128218608</v>
       </c>
       <c r="D5">
-        <v>0.32289600140652835</v>
+        <v>-0.12720257887581599</v>
       </c>
       <c r="E5">
-        <v>-6.5740576798610298E-2</v>
+        <v>-0.36959744953635709</v>
       </c>
       <c r="F5">
+        <v>-1.8723646338146007</v>
+      </c>
+      <c r="G5">
+        <v>-0.25820629583405319</v>
+      </c>
+      <c r="H5">
+        <v>1.4759296476124488</v>
+      </c>
+      <c r="I5">
         <v>-0.51982270831222288</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J5">
+        <v>0.28560410081019305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>-5.2137953989683239E-2</v>
+        <v>-7.9610767730242657E-2</v>
       </c>
       <c r="C6">
-        <v>0.19511425606610328</v>
+        <v>-0.15738585728116994</v>
       </c>
       <c r="D6">
-        <v>-0.10875618694641913</v>
+        <v>-0.49325701444921011</v>
       </c>
       <c r="E6">
-        <v>-7.9610767730242657E-2</v>
+        <v>-0.34121548286524195</v>
       </c>
       <c r="F6">
+        <v>-0.21033011176879368</v>
+      </c>
+      <c r="G6">
+        <v>-0.5128309443614818</v>
+      </c>
+      <c r="H6">
+        <v>0.27579016255209843</v>
+      </c>
+      <c r="I6">
         <v>-0.83214832203903222</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J6">
+        <v>-0.69547846787473533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>8.7817672606875563E-2</v>
+        <v>6.969627973402967E-2</v>
       </c>
       <c r="C7">
-        <v>0.21027463358278045</v>
+        <v>-0.85927754591652672</v>
       </c>
       <c r="D7">
-        <v>1.420047744445321</v>
+        <v>-1.1399831108347083</v>
       </c>
       <c r="E7">
-        <v>6.969627973402967E-2</v>
+        <v>-0.83829825532762992</v>
       </c>
       <c r="F7">
+        <v>-5.5599526337193006E-2</v>
+      </c>
+      <c r="G7">
+        <v>-0.1060335231392997</v>
+      </c>
+      <c r="H7">
+        <v>-0.88679726193623476</v>
+      </c>
+      <c r="I7">
         <v>0.77779739314375673</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J7">
+        <v>-0.30368566535492542</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.17277201255977004</v>
+        <v>0.10002553081165053</v>
       </c>
       <c r="C8">
-        <v>0.12171729230319009</v>
+        <v>0.68939299432538137</v>
       </c>
       <c r="D8">
-        <v>0.66140164444855976</v>
+        <v>0.89417227348618589</v>
       </c>
       <c r="E8">
-        <v>0.10002553081165053</v>
+        <v>1.0361397422384688</v>
       </c>
       <c r="F8">
+        <v>-0.43772752789538094</v>
+      </c>
+      <c r="G8">
+        <v>0.76642436555754245</v>
+      </c>
+      <c r="H8">
+        <v>0.41972788113853821</v>
+      </c>
+      <c r="I8">
         <v>-0.45482771109046571</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J8">
+        <v>1.3147774472695015</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>9.9366953395983559E-2</v>
+        <v>9.0816030217750227E-2</v>
       </c>
       <c r="C9">
-        <v>0.22579012963784356</v>
+        <v>-0.28136269006233111</v>
       </c>
       <c r="D9">
-        <v>0.50831715225603202</v>
+        <v>-1.2115803530209457</v>
       </c>
       <c r="E9">
-        <v>9.0816030217750227E-2</v>
+        <v>-6.7159371029392734E-3</v>
       </c>
       <c r="F9">
+        <v>1.5349736856657497</v>
+      </c>
+      <c r="G9">
+        <v>-1.006133798268483</v>
+      </c>
+      <c r="H9">
+        <v>-0.91071231828201826</v>
+      </c>
+      <c r="I9">
         <v>-5.089074018025086E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J9">
+        <v>-0.29855988174500742</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>-0.15298895321673844</v>
+        <v>-0.12919684870766704</v>
       </c>
       <c r="C10">
-        <v>0.27822414118626942</v>
+        <v>1.4701091881031916</v>
       </c>
       <c r="D10">
-        <v>-0.14301418274302372</v>
+        <v>1.1785301575727534</v>
       </c>
       <c r="E10">
-        <v>-0.12919684870766704</v>
+        <v>1.2823556827959652</v>
       </c>
       <c r="F10">
+        <v>1.1826633834694316</v>
+      </c>
+      <c r="G10">
+        <v>0.80293407022761132</v>
+      </c>
+      <c r="H10">
+        <v>0.69023148822897074</v>
+      </c>
+      <c r="I10">
         <v>-0.42158333622445754</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J10">
+        <v>0.54899146287389622</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>4.3962461059786184E-2</v>
+        <v>-1.9385703075541647E-2</v>
       </c>
       <c r="C11">
-        <v>0.1369536980908376</v>
+        <v>-3.4425864018796659E-2</v>
       </c>
       <c r="D11">
-        <v>1.5097030304835677</v>
+        <v>1.0537017070309402</v>
       </c>
       <c r="E11">
-        <v>-1.9385703075541647E-2</v>
+        <v>0.9440543983345242</v>
       </c>
       <c r="F11">
+        <v>0.91272929969230687</v>
+      </c>
+      <c r="G11">
+        <v>0.69606988359002475</v>
+      </c>
+      <c r="H11">
+        <v>0.27796582672252512</v>
+      </c>
+      <c r="I11">
         <v>0.4750223793098507</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J11">
+        <v>0.80784888931032239</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>-0.15257021013677663</v>
+        <v>-0.1713331280356554</v>
       </c>
       <c r="C12">
-        <v>0.20923460322604251</v>
+        <v>-1.8225648270614656</v>
       </c>
       <c r="D12">
-        <v>0.67678285259909754</v>
+        <v>-0.31122625328767939</v>
       </c>
       <c r="E12">
-        <v>-0.1713331280356554</v>
+        <v>-1.623177271069409</v>
       </c>
       <c r="F12">
+        <v>0.59427903018370776</v>
+      </c>
+      <c r="G12">
+        <v>-0.87406183740180576</v>
+      </c>
+      <c r="H12">
+        <v>-0.3264331945962573</v>
+      </c>
+      <c r="I12">
         <v>2.8966022609933084E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J12">
+        <v>-2.5518978592406603</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>-0.20687697906651215</v>
+        <v>-0.16030959325557864</v>
       </c>
       <c r="C13">
-        <v>0.31514707166594219</v>
+        <v>-1.4754730816397199</v>
       </c>
       <c r="D13">
-        <v>-0.81383598787828504</v>
+        <v>-1.0294326517232331</v>
       </c>
       <c r="E13">
-        <v>-0.16030959325557864</v>
+        <v>0.89719628168059229</v>
       </c>
       <c r="F13">
+        <v>0.97188887381410138</v>
+      </c>
+      <c r="G13">
+        <v>-2.0952639382190941E-2</v>
+      </c>
+      <c r="H13">
+        <v>-2.353674589859462</v>
+      </c>
+      <c r="I13">
         <v>-0.89478523126066012</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J13">
+        <v>-1.8066678088589656</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>9.5199353727572378E-2</v>
+        <v>9.2803368574188028E-2</v>
       </c>
       <c r="C14">
-        <v>0.23576841907304863</v>
+        <v>1.234263999607135</v>
       </c>
       <c r="D14">
-        <v>1.1182254705315671</v>
+        <v>-0.51862064572136501</v>
       </c>
       <c r="E14">
-        <v>9.2803368574188028E-2</v>
+        <v>-0.10648223042420157</v>
       </c>
       <c r="F14">
+        <v>-1.7617090622160949</v>
+      </c>
+      <c r="G14">
+        <v>-0.19894862335160002</v>
+      </c>
+      <c r="H14">
+        <v>-0.6858100096091343</v>
+      </c>
+      <c r="I14">
         <v>0.61242364948534389</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J14">
+        <v>-0.49187724512771769</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>2.704689402527638E-2</v>
+        <v>5.6132955994103423E-2</v>
       </c>
       <c r="C15">
-        <v>0.28680662237094401</v>
+        <v>-0.10328095002601384</v>
       </c>
       <c r="D15">
-        <v>0.31932303618224911</v>
+        <v>-1.1510311789425811</v>
       </c>
       <c r="E15">
-        <v>5.6132955994103423E-2</v>
+        <v>-2.5034006528693644</v>
       </c>
       <c r="F15">
+        <v>-2.2651904848547542</v>
+      </c>
+      <c r="G15">
+        <v>-0.54395884584510468</v>
+      </c>
+      <c r="H15">
+        <v>6.583129457682238E-2</v>
+      </c>
+      <c r="I15">
         <v>8.668927130914883E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J15">
+        <v>0.56521810967735808</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>9.8218343483025272E-3</v>
+        <v>5.0825305046034719E-2</v>
       </c>
       <c r="C16">
-        <v>0.30612693934807106</v>
+        <v>-6.1438344707866882E-2</v>
       </c>
       <c r="D16">
-        <v>1.3036376173985698</v>
+        <v>0.1489195399694993</v>
       </c>
       <c r="E16">
-        <v>5.0825305046034719E-2</v>
+        <v>-5.9980822389219424E-2</v>
       </c>
       <c r="F16">
+        <v>5.7490157068011971E-2</v>
+      </c>
+      <c r="G16">
+        <v>0.94704780080890938</v>
+      </c>
+      <c r="H16">
+        <v>-1.4579235695066517</v>
+      </c>
+      <c r="I16">
         <v>1.1744105771408719</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J16">
+        <v>0.91689840515659571</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>3.8038115405133466E-2</v>
+        <v>6.7567196809390273E-2</v>
       </c>
       <c r="C17">
-        <v>0.28752483856325861</v>
+        <v>8.6762241692722231E-2</v>
       </c>
       <c r="D17">
-        <v>0.27582154735994968</v>
+        <v>-1.1629488652032891</v>
       </c>
       <c r="E17">
-        <v>6.7567196809390273E-2</v>
+        <v>1.8667456231234332</v>
       </c>
       <c r="F17">
+        <v>0.5093845663044525</v>
+      </c>
+      <c r="G17">
+        <v>0.14268841761275153</v>
+      </c>
+      <c r="H17">
+        <v>-0.99755298461377995</v>
+      </c>
+      <c r="I17">
         <v>4.7031838673967208E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J17">
+        <v>-0.91776476801971696</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>3.1983028498378197E-2</v>
+        <v>1.727308791200674E-2</v>
       </c>
       <c r="C18">
-        <v>0.21580522677013736</v>
+        <v>1.893165102312425</v>
       </c>
       <c r="D18">
-        <v>1.6378169200640726</v>
+        <v>1.4584044473904791</v>
       </c>
       <c r="E18">
-        <v>1.727308791200674E-2</v>
+        <v>-0.74562985321880004</v>
       </c>
       <c r="F18">
+        <v>0.57729078321839311</v>
+      </c>
+      <c r="G18">
+        <v>0.26966963243269459</v>
+      </c>
+      <c r="H18">
+        <v>0.4513668046869222</v>
+      </c>
+      <c r="I18">
         <v>1.025167559644899</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J18">
+        <v>1.6966748499162332</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>7.5822081550788845E-2</v>
+        <v>8.2829610946688864E-2</v>
       </c>
       <c r="C19">
-        <v>0.25101325005300368</v>
+        <v>-1.0884737140233445</v>
       </c>
       <c r="D19">
-        <v>0.45438291944758502</v>
+        <v>-0.59833500103882353</v>
       </c>
       <c r="E19">
-        <v>8.2829610946688864E-2</v>
+        <v>5.4800912587781192E-2</v>
       </c>
       <c r="F19">
+        <v>1.2173050171419013</v>
+      </c>
+      <c r="G19">
+        <v>0.27803280114076767</v>
+      </c>
+      <c r="H19">
+        <v>-0.64545764760368796</v>
+      </c>
+      <c r="I19">
         <v>3.017489630948389E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J19">
+        <v>-0.58177099546985955</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>4.3427951548348442E-2</v>
+        <v>0.12951899452263768</v>
       </c>
       <c r="C20">
-        <v>0.37922220761720221</v>
+        <v>1.3796414697922921</v>
       </c>
       <c r="D20">
-        <v>0.4538445694671861</v>
+        <v>2.0373358372975177</v>
       </c>
       <c r="E20">
-        <v>0.12951899452263768</v>
+        <v>1.0407283606972741</v>
       </c>
       <c r="F20">
+        <v>0.12906740357594301</v>
+      </c>
+      <c r="G20">
+        <v>0.59437574944425964</v>
+      </c>
+      <c r="H20">
+        <v>2.6159147359165962</v>
+      </c>
+      <c r="I20">
         <v>0.71584000685017124</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="J20">
+        <v>1.6408415401645033</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>-4.7473979220849616E-2</v>
+        <v>-1.2750344358779253E-2</v>
       </c>
       <c r="C21">
-        <v>0.29594616753187653</v>
+        <v>1.0333625583929709</v>
       </c>
       <c r="D21">
-        <v>1.1484776471306326</v>
+        <v>0.83221768243367689</v>
       </c>
       <c r="E21">
-        <v>-1.2750344358779253E-2</v>
+        <v>3.8551229624648538</v>
       </c>
       <c r="F21">
+        <v>1.5900265188779144</v>
+      </c>
+      <c r="G21">
+        <v>0.78333188012533261</v>
+      </c>
+      <c r="H21">
+        <v>0.1474334173733729</v>
+      </c>
+      <c r="I21">
         <v>0.96476080379072759</v>
+      </c>
+      <c r="J21">
+        <v>-7.3498446592665578E-2</v>
       </c>
     </row>
   </sheetData>
@@ -1478,28 +1747,33 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" customWidth="1"/>
-    <col min="4" max="5" width="16.08984375" customWidth="1"/>
-    <col min="6" max="6" width="13.90625" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.26953125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
         <v>10</v>
       </c>
-      <c r="C1" t="s">
-        <v>9</v>
-      </c>
       <c r="D1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -1507,405 +1781,657 @@
       <c r="F1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.24367326534378794</v>
+        <v>-3.3476077421254469E-4</v>
       </c>
       <c r="C2">
-        <v>1.5890327155864359E-2</v>
+        <v>-0.23432116728379737</v>
       </c>
       <c r="D2">
-        <v>1.3115675136983991</v>
+        <v>0.73883650134770817</v>
       </c>
       <c r="E2">
-        <v>-3.3476077421254469E-4</v>
+        <v>0.92977263128754761</v>
       </c>
       <c r="F2">
-        <v>0.73883650134770817</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.35665575685102746</v>
+      </c>
+      <c r="G2">
+        <v>-8.9223542749104268E-2</v>
+      </c>
+      <c r="H2">
+        <v>0.89330871119003863</v>
+      </c>
+      <c r="I2">
+        <v>-0.166949871410913</v>
+      </c>
+      <c r="J2">
+        <v>-0.42974764101380808</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.30411797708162736</v>
+        <v>5.5953274979683859E-2</v>
       </c>
       <c r="C3">
-        <v>-2.0174117386022594E-3</v>
+        <v>-1.6224989147796036</v>
       </c>
       <c r="D3">
-        <v>-0.70709219391300648</v>
+        <v>-1.2261887243479914</v>
       </c>
       <c r="E3">
-        <v>5.5953274979683859E-2</v>
+        <v>-2.1937444581812189</v>
       </c>
       <c r="F3">
-        <v>-1.2261887243479914</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>-0.6948946930447516</v>
+      </c>
+      <c r="G3">
+        <v>-0.33333702777725721</v>
+      </c>
+      <c r="H3">
+        <v>-0.66538128812119834</v>
+      </c>
+      <c r="I3">
+        <v>-1.2906661498741923</v>
+      </c>
+      <c r="J3">
+        <v>-1.5896501175561826</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.30953061719874286</v>
+        <v>1.1144298117685247E-2</v>
       </c>
       <c r="C4">
-        <v>-0.21838154673349786</v>
+        <v>-0.10076051732192315</v>
       </c>
       <c r="D4">
-        <v>-0.27313005362059284</v>
+        <v>-0.14420628657531886</v>
       </c>
       <c r="E4">
-        <v>1.1144298117685247E-2</v>
+        <v>-2.7203015738048077</v>
       </c>
       <c r="F4">
-        <v>-0.14420628657531886</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>-2.686835452758634</v>
+      </c>
+      <c r="G4">
+        <v>-1.274075314187912</v>
+      </c>
+      <c r="H4">
+        <v>1.6616409324285426</v>
+      </c>
+      <c r="I4">
+        <v>-0.98116533702517894</v>
+      </c>
+      <c r="J4">
+        <v>2.1001000654749395</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.17281950440322735</v>
+        <v>-8.0567397046981126E-2</v>
       </c>
       <c r="C5">
-        <v>-2.4515624912984091E-2</v>
+        <v>0.74732276424162203</v>
       </c>
       <c r="D5">
-        <v>1.3021439166084747</v>
+        <v>0.8504305446363335</v>
       </c>
       <c r="E5">
-        <v>-8.0567397046981126E-2</v>
+        <v>-0.1362415375231163</v>
       </c>
       <c r="F5">
-        <v>0.8504305446363335</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+        <v>-1.2945775013349734</v>
+      </c>
+      <c r="G5">
+        <v>0.20736721540701053</v>
+      </c>
+      <c r="H5">
+        <v>1.2899172636965639</v>
+      </c>
+      <c r="I5">
+        <v>-2.0289098783425663E-2</v>
+      </c>
+      <c r="J5">
+        <v>0.81048903370157044</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.19511425606610328</v>
+        <v>-6.4684234952744946E-2</v>
       </c>
       <c r="C6">
-        <v>-5.2137953989683239E-2</v>
+        <v>0.37080015821292167</v>
       </c>
       <c r="D6">
-        <v>0.66653459273094651</v>
+        <v>0.29755133638449566</v>
       </c>
       <c r="E6">
-        <v>-6.4684234952744946E-2</v>
+        <v>-6.2427746788056071E-2</v>
       </c>
       <c r="F6">
-        <v>0.29755133638449566</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.27331289907271716</v>
+      </c>
+      <c r="G6">
+        <v>-6.9721840928349044E-2</v>
+      </c>
+      <c r="H6">
+        <v>0.10964568864326341</v>
+      </c>
+      <c r="I6">
+        <v>-0.31684389131634338</v>
+      </c>
+      <c r="J6">
+        <v>-0.18579230982605582</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.21027463358278045</v>
+        <v>-1.7037891713652137E-2</v>
       </c>
       <c r="C7">
-        <v>8.7817672606875563E-2</v>
+        <v>-1.0333485392873665</v>
       </c>
       <c r="D7">
-        <v>-0.1634881794798824</v>
+        <v>-0.95164482046920718</v>
       </c>
       <c r="E7">
-        <v>-1.7037891713652137E-2</v>
+        <v>-1.0738476907198988</v>
       </c>
       <c r="F7">
-        <v>-0.95164482046920718</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5.0136914728459159E-3</v>
+      </c>
+      <c r="G7">
+        <v>-0.22356377711133546</v>
+      </c>
+      <c r="H7">
+        <v>-0.87377941237158063</v>
+      </c>
+      <c r="I7">
+        <v>0.5274543768833253</v>
+      </c>
+      <c r="J7">
+        <v>-0.46774400966986279</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.12171729230319009</v>
+        <v>-8.5875955942411625E-2</v>
       </c>
       <c r="C8">
-        <v>0.17277201255977004</v>
+        <v>0.67999003042919703</v>
       </c>
       <c r="D8">
-        <v>2.9413705074877923</v>
+        <v>1.8987718045097164</v>
       </c>
       <c r="E8">
-        <v>-8.5875955942411625E-2</v>
+        <v>0.70519101534280271</v>
       </c>
       <c r="F8">
-        <v>1.8987718045097164</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+        <v>5.2846364787527023E-2</v>
+      </c>
+      <c r="G8">
+        <v>0.82320726902475228</v>
+      </c>
+      <c r="H8">
+        <v>0.32798476512154595</v>
+      </c>
+      <c r="I8">
+        <v>-0.64669289462496793</v>
+      </c>
+      <c r="J8">
+        <v>1.3145885864151956</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.22579012963784356</v>
+        <v>1.1583793052861446E-3</v>
       </c>
       <c r="C9">
-        <v>9.9366953395983559E-2</v>
+        <v>-0.59961122048755389</v>
       </c>
       <c r="D9">
-        <v>-0.42267566125913963</v>
+        <v>-1.2454229166902588</v>
       </c>
       <c r="E9">
-        <v>1.1583793052861446E-3</v>
+        <v>-0.3163441497474121</v>
       </c>
       <c r="F9">
-        <v>-1.2454229166902588</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1.4604731183558355</v>
+      </c>
+      <c r="G9">
+        <v>-1.2450193442545507</v>
+      </c>
+      <c r="H9">
+        <v>-0.85175528864109906</v>
+      </c>
+      <c r="I9">
+        <v>-0.44076231949617706</v>
+      </c>
+      <c r="J9">
+        <v>-0.60180099324291403</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.27822414118626942</v>
+        <v>-4.9834987437955003E-3</v>
       </c>
       <c r="C10">
-        <v>-0.15298895321673844</v>
+        <v>1.9359120720050425</v>
       </c>
       <c r="D10">
-        <v>1.3334809780380894</v>
+        <v>1.266550991850482</v>
       </c>
       <c r="E10">
-        <v>-4.9834987437955003E-3</v>
+        <v>1.7232252039509239</v>
       </c>
       <c r="F10">
-        <v>1.266550991850482</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1.3105657631792125</v>
+      </c>
+      <c r="G10">
+        <v>1.1550211040405842</v>
+      </c>
+      <c r="H10">
+        <v>0.60036136795520112</v>
+      </c>
+      <c r="I10">
+        <v>0.14214787917544705</v>
+      </c>
+      <c r="J10">
+        <v>0.99316449346658198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.1369536980908376</v>
+        <v>-0.100538331479295</v>
       </c>
       <c r="C11">
-        <v>4.3962461059786184E-2</v>
+        <v>0.42605450568297187</v>
       </c>
       <c r="D11">
-        <v>2.9166840447377864</v>
+        <v>2.2598757311109194</v>
       </c>
       <c r="E11">
-        <v>-0.100538331479295</v>
+        <v>1.0217458266530288</v>
       </c>
       <c r="F11">
-        <v>2.2598757311109194</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1.5875929890231233</v>
+      </c>
+      <c r="G11">
+        <v>1.1151841780543523</v>
+      </c>
+      <c r="H11">
+        <v>8.5080546537637844E-2</v>
+      </c>
+      <c r="I11">
+        <v>0.83160007959487436</v>
+      </c>
+      <c r="J11">
+        <v>1.2567077040763674</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.20923460322604251</v>
+        <v>-7.3875839658980785E-2</v>
       </c>
       <c r="C12">
-        <v>-0.15257021013677663</v>
+        <v>-0.94155681912886524</v>
       </c>
       <c r="D12">
-        <v>0.67784317411368578</v>
+        <v>0.60965903360308471</v>
       </c>
       <c r="E12">
-        <v>-7.3875839658980785E-2</v>
+        <v>-1.0307436431885835</v>
       </c>
       <c r="F12">
-        <v>0.60965903360308471</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1.2058723245902216</v>
+      </c>
+      <c r="G12">
+        <v>-0.1602393741516755</v>
+      </c>
+      <c r="H12">
+        <v>-0.56654418695462105</v>
+      </c>
+      <c r="I12">
+        <v>0.95989689389398447</v>
+      </c>
+      <c r="J12">
+        <v>-1.7052202076517566</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.31514707166594219</v>
+        <v>1.943114890955866E-2</v>
       </c>
       <c r="C13">
-        <v>-0.20687697906651215</v>
+        <v>-0.99775518977399924</v>
       </c>
       <c r="D13">
-        <v>-1.3208988423916121</v>
+        <v>-1.2264317719800837</v>
       </c>
       <c r="E13">
-        <v>1.943114890955866E-2</v>
+        <v>1.4412723699446039</v>
       </c>
       <c r="F13">
-        <v>-1.2264317719800837</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.96229094805040094</v>
+      </c>
+      <c r="G13">
+        <v>0.32190302553776662</v>
+      </c>
+      <c r="H13">
+        <v>-2.4191374908225054</v>
+      </c>
+      <c r="I13">
+        <v>-0.26511425515971365</v>
+      </c>
+      <c r="J13">
+        <v>-1.3536385919809235</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14">
-        <v>0.23576841907304863</v>
+        <v>1.0169301416539073E-2</v>
       </c>
       <c r="C14">
-        <v>9.5199353727572378E-2</v>
+        <v>0.87388099904105587</v>
       </c>
       <c r="D14">
-        <v>0.14964145109950891</v>
+        <v>-0.66062365622991071</v>
       </c>
       <c r="E14">
-        <v>1.0169301416539073E-2</v>
+        <v>-0.42392518002841106</v>
       </c>
       <c r="F14">
-        <v>-0.66062365622991071</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+        <v>-1.8968794889001894</v>
+      </c>
+      <c r="G14">
+        <v>-0.47604355901004114</v>
+      </c>
+      <c r="H14">
+        <v>-0.60940882435027521</v>
+      </c>
+      <c r="I14">
+        <v>0.18952921340472129</v>
+      </c>
+      <c r="J14">
+        <v>-0.83617020253675489</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15">
-        <v>0.28680662237094401</v>
+        <v>4.5388215961083694E-2</v>
       </c>
       <c r="C15">
-        <v>2.704689402527638E-2</v>
+        <v>-0.47483925571170466</v>
       </c>
       <c r="D15">
-        <v>-1.0998469216616884</v>
+        <v>-1.7059923526346954</v>
       </c>
       <c r="E15">
-        <v>4.5388215961083694E-2</v>
+        <v>-2.6999463384104549</v>
       </c>
       <c r="F15">
-        <v>-1.7059923526346954</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+        <v>-2.6047570336987942</v>
+      </c>
+      <c r="G15">
+        <v>-0.85558367490563692</v>
+      </c>
+      <c r="H15">
+        <v>0.18258273315887635</v>
+      </c>
+      <c r="I15">
+        <v>-0.27604796806878207</v>
+      </c>
+      <c r="J15">
+        <v>0.20668543604225176</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16">
-        <v>0.30612693934807106</v>
+        <v>6.0710317847896572E-2</v>
       </c>
       <c r="C16">
-        <v>9.8218343483025272E-3</v>
+        <v>-0.47463376210956398</v>
       </c>
       <c r="D16">
-        <v>-3.3488662693525836E-2</v>
+        <v>-0.58804426665453235</v>
       </c>
       <c r="E16">
-        <v>6.0710317847896572E-2</v>
+        <v>-0.24021029953719775</v>
       </c>
       <c r="F16">
-        <v>-0.58804426665453235</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+        <v>-0.37884071289475141</v>
+      </c>
+      <c r="G16">
+        <v>0.5928956443417609</v>
+      </c>
+      <c r="H16">
+        <v>-1.316950493850364</v>
+      </c>
+      <c r="I16">
+        <v>0.7925122500285634</v>
+      </c>
+      <c r="J16">
+        <v>0.51714328820599897</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17">
-        <v>0.28752483856325861</v>
+        <v>4.865767249775968E-2</v>
       </c>
       <c r="C17">
-        <v>3.8038115405133466E-2</v>
+        <v>-0.3370913566953318</v>
       </c>
       <c r="D17">
-        <v>-1.1204482070234327</v>
+        <v>-1.7595128394547332</v>
       </c>
       <c r="E17">
-        <v>4.865767249775968E-2</v>
+        <v>1.6308548131991134</v>
       </c>
       <c r="F17">
-        <v>-1.7595128394547332</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.13991435666468188</v>
+      </c>
+      <c r="G17">
+        <v>-0.2104787328076444</v>
+      </c>
+      <c r="H17">
+        <v>-0.86776299780282284</v>
+      </c>
+      <c r="I17">
+        <v>-0.37330616151859619</v>
+      </c>
+      <c r="J17">
+        <v>-1.326441033230064</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18">
-        <v>0.21580522677013736</v>
+        <v>-2.4467422951021445E-2</v>
       </c>
       <c r="C18">
-        <v>3.1983028498378197E-2</v>
+        <v>1.929264317818578</v>
       </c>
       <c r="D18">
-        <v>2.3680316938562198</v>
+        <v>1.7471023185398609</v>
       </c>
       <c r="E18">
-        <v>-2.4467422951021445E-2</v>
+        <v>-0.80166579995807197</v>
       </c>
       <c r="F18">
-        <v>1.7471023185398609</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0.72533128069932695</v>
+      </c>
+      <c r="G18">
+        <v>0.31485106231764548</v>
+      </c>
+      <c r="H18">
+        <v>0.41819747148724029</v>
+      </c>
+      <c r="I18">
+        <v>1.018303892492638</v>
+      </c>
+      <c r="J18">
+        <v>1.7335562605180495</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19">
-        <v>0.25101325005300368</v>
+        <v>2.0916353957450035E-2</v>
       </c>
       <c r="C19">
-        <v>7.5822081550788845E-2</v>
+        <v>-1.4564681634318621</v>
       </c>
       <c r="D19">
-        <v>-0.11439066537336177</v>
+        <v>-0.86661997263521717</v>
       </c>
       <c r="E19">
-        <v>2.0916353957450035E-2</v>
+        <v>-0.22989501981739069</v>
       </c>
       <c r="F19">
-        <v>-0.86661997263521717</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+        <v>1.018867317413104</v>
+      </c>
+      <c r="G19">
+        <v>-1.2741175642745239E-2</v>
+      </c>
+      <c r="H19">
+        <v>-0.55598191088030313</v>
+      </c>
+      <c r="I19">
+        <v>-0.37954149559778916</v>
+      </c>
+      <c r="J19">
+        <v>-0.93441082773263129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20">
-        <v>0.37922220761720221</v>
+        <v>0.14160610973992735</v>
       </c>
       <c r="C20">
-        <v>4.3427951548348442E-2</v>
+        <v>0.37797475471574926</v>
       </c>
       <c r="D20">
-        <v>0.97116865979670164</v>
+        <v>0.3159612261521666</v>
       </c>
       <c r="E20">
-        <v>0.14160610973992735</v>
+        <v>0.58296175379332693</v>
       </c>
       <c r="F20">
-        <v>0.3159612261521666</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+        <v>-0.89674877108192763</v>
+      </c>
+      <c r="G20">
+        <v>-0.26002116097497785</v>
+      </c>
+      <c r="H20">
+        <v>2.9516026020331498</v>
+      </c>
+      <c r="I20">
+        <v>-0.22164416149690325</v>
+      </c>
+      <c r="J20">
+        <v>0.67232515373769197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21">
-        <v>0.29594616753187653</v>
+        <v>3.7230260530227544E-2</v>
       </c>
       <c r="C21">
-        <v>-4.7473979220849616E-2</v>
+        <v>0.93168530386443527</v>
       </c>
       <c r="D21">
-        <v>0.77290018969471963</v>
+        <v>0.38994811953718456</v>
       </c>
       <c r="E21">
-        <v>3.7230260530227544E-2</v>
+        <v>3.8942698235332802</v>
       </c>
       <c r="F21">
-        <v>0.38994811953718456</v>
+        <v>1.354796843553999</v>
+      </c>
+      <c r="G21">
+        <v>0.67961902577736188</v>
+      </c>
+      <c r="H21">
+        <v>0.20637981154270973</v>
+      </c>
+      <c r="I21">
+        <v>0.91757901889943039</v>
+      </c>
+      <c r="J21">
+        <v>-0.17414408719769281</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/Source_Data_7T_Fig4_5.xlsx
+++ b/source_data/Source_Data_7T_Fig4_5.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zyeon\Desktop\Spatial 분석\paper\NC_final_revision\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Spatial\code\paper\KIM_code_availability_NC\source_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E594D50-5CE2-4D32-8345-4000EBA5B7E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FB08E41-56F2-4E0F-961C-E44EAD7F3986}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17610" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Fig4e_on_off_retrieval" sheetId="2" r:id="rId1"/>
-    <sheet name="Fig4g_AntSub_corr" sheetId="3" r:id="rId2"/>
-    <sheet name="Fig5b_PostDG_corr" sheetId="4" r:id="rId3"/>
+    <sheet name="Fig4g_corr" sheetId="3" r:id="rId2"/>
+    <sheet name="Fig5b_corr" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
